--- a/project/evaluations/LLM_Bert_Scores.xlsx
+++ b/project/evaluations/LLM_Bert_Scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I360"/>
+  <dimension ref="A1:H360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,11 +469,6 @@
           <t>Assistance_Required_Match</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LLM_BLEU_Score</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -507,16 +502,7 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,11 +542,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -601,11 +582,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -645,11 +621,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -689,11 +660,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -731,11 +697,6 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -777,11 +738,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -821,11 +777,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -865,11 +816,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -909,11 +855,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -953,11 +894,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -997,11 +933,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1039,11 +970,6 @@
       <c r="H14" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -1085,11 +1011,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1129,11 +1050,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1171,11 +1087,6 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -1217,11 +1128,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1261,11 +1167,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1305,11 +1206,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1349,11 +1245,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1393,11 +1284,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1437,11 +1323,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1479,11 +1360,6 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -1525,11 +1401,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1569,11 +1440,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1613,11 +1479,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1657,11 +1518,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1699,11 +1555,6 @@
       <c r="H29" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -1745,11 +1596,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1789,11 +1635,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1833,11 +1674,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1875,11 +1711,6 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -1921,11 +1752,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1965,11 +1791,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2009,11 +1830,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2053,11 +1869,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2097,11 +1908,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2139,11 +1945,6 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -2185,11 +1986,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2229,11 +2025,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2273,11 +2064,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2315,11 +2101,6 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -2361,11 +2142,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2405,11 +2181,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2449,11 +2220,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2491,11 +2257,6 @@
       <c r="H47" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -2537,11 +2298,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2579,11 +2335,6 @@
       <c r="H49" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -2625,11 +2376,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2669,11 +2415,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2713,11 +2454,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2757,11 +2493,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2801,11 +2532,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>BLEU = 0.75 5.9/0.7/0.4/0.2 (BP = 1.000 ratio = 68.000 hyp_len = 68 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2844,11 +2570,6 @@
       <c r="H55" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -2891,11 +2612,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2936,11 +2652,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2981,11 +2692,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3026,11 +2732,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3069,11 +2770,6 @@
       <c r="H60" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -3114,11 +2810,6 @@
       <c r="H61" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -3164,11 +2855,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3209,11 +2895,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3254,11 +2935,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3299,11 +2975,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>BLEU = 0.56 5.9/0.5/0.3/0.1 (BP = 1.000 ratio = 101.000 hyp_len = 101 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3343,11 +3014,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3387,11 +3053,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3431,11 +3092,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3473,11 +3129,6 @@
       <c r="H69" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -3519,11 +3170,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3563,11 +3209,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3605,11 +3246,6 @@
       <c r="H72" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -3651,11 +3287,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3695,11 +3326,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3739,11 +3365,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3783,11 +3404,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3827,11 +3443,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3871,11 +3482,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3915,11 +3521,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3959,11 +3560,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4001,11 +3597,6 @@
       <c r="H81" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -4043,16 +3634,7 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4090,11 +3672,6 @@
       <c r="H83" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -4136,11 +3713,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4180,11 +3752,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4224,11 +3791,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4266,11 +3828,6 @@
       <c r="H87" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -4312,11 +3869,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4354,11 +3906,6 @@
       <c r="H89" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -4399,11 +3946,6 @@
       <c r="H90" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -4446,11 +3988,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4490,11 +4027,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4534,11 +4066,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4576,11 +4103,6 @@
       <c r="H94" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -4622,11 +4144,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4664,11 +4181,6 @@
       <c r="H96" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -4711,11 +4223,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4755,11 +4262,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4799,11 +4301,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4841,11 +4338,6 @@
       <c r="H100" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -4887,11 +4379,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4931,11 +4418,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4969,16 +4451,7 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5012,16 +4485,7 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5056,16 +4520,7 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>BLEU = 0.32 3.4/0.3/0.1/0.1 (BP = 1.000 ratio = 176.000 hyp_len = 176 ref_len = 1)</t>
-        </is>
-      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5108,11 +4563,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5153,11 +4603,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5198,11 +4643,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5241,11 +4681,6 @@
       <c r="H109" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -5288,11 +4723,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5333,11 +4763,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5378,11 +4803,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5421,11 +4841,6 @@
       <c r="H113" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -5471,11 +4886,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5516,11 +4926,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5559,11 +4964,6 @@
       <c r="H116" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -5606,11 +5006,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5651,11 +5046,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5696,11 +5086,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5741,11 +5126,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5784,11 +5164,6 @@
       <c r="H121" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -5826,16 +5201,7 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5876,11 +5242,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5921,11 +5282,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5966,11 +5322,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6011,11 +5362,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6054,11 +5400,6 @@
       <c r="H127" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -6101,11 +5442,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6146,11 +5482,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6189,11 +5520,6 @@
       <c r="H130" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -6236,11 +5562,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6279,11 +5600,6 @@
       <c r="H132" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -6330,11 +5646,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6375,11 +5686,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6418,11 +5724,6 @@
       <c r="H135" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -6468,11 +5769,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6513,11 +5809,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6556,11 +5847,6 @@
       <c r="H138" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -6601,11 +5887,6 @@
       <c r="H139" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -6652,11 +5933,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6697,11 +5973,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6742,11 +6013,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6787,11 +6053,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6832,11 +6093,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6877,11 +6133,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6920,11 +6171,6 @@
       <c r="H146" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -6967,11 +6213,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7012,11 +6253,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7057,11 +6293,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7100,11 +6331,6 @@
       <c r="H150" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -7147,11 +6373,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7192,11 +6413,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7237,11 +6453,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7282,11 +6493,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7325,11 +6531,6 @@
       <c r="H155" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -7372,11 +6573,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7417,11 +6613,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7460,11 +6651,6 @@
       <c r="H158" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -7508,11 +6694,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7551,11 +6732,6 @@
       <c r="H160" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -7598,11 +6774,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7643,11 +6814,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7688,11 +6854,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7733,11 +6894,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7778,11 +6934,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7821,11 +6972,6 @@
       <c r="H166" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -7868,11 +7014,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7913,11 +7054,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7956,11 +7092,6 @@
       <c r="H169" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8003,11 +7134,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8048,11 +7174,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>BLEU = 0.37 3.9/0.3/0.2/0.1 (BP = 1.000 ratio = 153.000 hyp_len = 153 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8092,11 +7213,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8134,11 +7250,6 @@
       <c r="H173" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8178,11 +7289,6 @@
       <c r="H174" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8225,11 +7331,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8269,11 +7370,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8313,11 +7409,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8356,11 +7447,6 @@
       <c r="H178" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8403,11 +7489,6 @@
           <t>False Positive</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8445,11 +7526,6 @@
       <c r="H180" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8491,11 +7567,6 @@
       <c r="H181" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8541,11 +7612,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8583,11 +7649,6 @@
       <c r="H183" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8630,11 +7691,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8672,11 +7728,6 @@
       <c r="H185" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8719,11 +7770,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8761,11 +7807,6 @@
       <c r="H187" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8807,11 +7848,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8849,11 +7885,6 @@
       <c r="H189" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8894,11 +7925,6 @@
       <c r="H190" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -8944,11 +7970,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8986,11 +8007,6 @@
       <c r="H192" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -9032,11 +8048,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9076,11 +8087,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9120,11 +8126,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9164,11 +8165,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9208,11 +8204,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9250,11 +8241,6 @@
       <c r="H198" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -9297,11 +8283,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9339,11 +8320,6 @@
       <c r="H200" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -9386,11 +8362,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9431,11 +8402,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9473,11 +8439,6 @@
       <c r="H203" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -9521,11 +8482,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9566,11 +8522,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9611,11 +8562,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9653,11 +8599,6 @@
       <c r="H207" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -9701,11 +8642,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9745,11 +8681,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9787,11 +8718,6 @@
       <c r="H210" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -9833,11 +8759,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9877,11 +8798,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9921,11 +8837,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9963,11 +8874,6 @@
       <c r="H214" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -10009,11 +8915,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.7/0.4/0.2/0.1 (BP = 1.000 ratio = 135.000 hyp_len = 135 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10054,11 +8955,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10097,11 +8993,6 @@
       <c r="H217" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -10144,11 +9035,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10187,11 +9073,6 @@
       <c r="H219" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -10234,11 +9115,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10279,11 +9155,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10324,11 +9195,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10367,11 +9233,6 @@
       <c r="H223" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -10414,11 +9275,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10459,11 +9315,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10504,11 +9355,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10549,11 +9395,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10594,11 +9435,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10639,11 +9475,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10682,11 +9513,6 @@
       <c r="H230" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -10729,11 +9555,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10774,11 +9595,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10817,11 +9633,6 @@
       <c r="H233" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -10866,11 +9677,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10910,11 +9716,6 @@
       <c r="H235" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -10958,11 +9759,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11005,11 +9801,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11051,11 +9842,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11095,11 +9881,6 @@
       <c r="H239" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -11146,11 +9927,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>BLEU = 0.74 7.9/0.7/0.3/0.2 (BP = 1.000 ratio = 76.000 hyp_len = 76 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11191,11 +9967,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11234,11 +10005,6 @@
       <c r="H242" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -11281,11 +10047,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11326,11 +10087,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11371,11 +10127,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11414,11 +10165,6 @@
       <c r="H246" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -11461,11 +10207,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11506,11 +10247,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11551,11 +10287,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11596,11 +10327,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>BLEU = 0.61 6.5/0.5/0.3/0.1 (BP = 1.000 ratio = 92.000 hyp_len = 92 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11639,11 +10365,6 @@
       <c r="H251" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -11686,11 +10407,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11731,11 +10447,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11776,11 +10487,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11821,11 +10527,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -11866,11 +10567,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -11911,11 +10607,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11954,11 +10645,6 @@
       <c r="H258" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -12001,11 +10687,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12046,11 +10727,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>BLEU = 0.82 8.7/0.7/0.4/0.2 (BP = 1.000 ratio = 69.000 hyp_len = 69 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12091,11 +10767,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12136,11 +10807,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12179,11 +10845,6 @@
       <c r="H263" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -12226,11 +10887,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12269,11 +10925,6 @@
       <c r="H265" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -12316,11 +10967,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12361,11 +11007,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12404,11 +11045,6 @@
       <c r="H268" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -12451,11 +11087,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12494,11 +11125,6 @@
       <c r="H270" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.1/0.5/0.3/0.1 (BP = 1.000 ratio = 98.000 hyp_len = 98 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -12541,11 +11167,6 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12584,11 +11205,6 @@
       <c r="H272" t="inlineStr">
         <is>
           <t>False Negative</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -12632,11 +11248,6 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -12677,11 +11288,6 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12720,11 +11326,6 @@
       <c r="H275" t="inlineStr">
         <is>
           <t>False Negative</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -12768,11 +11369,6 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -12813,11 +11409,6 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -12858,11 +11449,6 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12903,11 +11489,6 @@
           <t>False Negative</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12946,11 +11527,6 @@
       <c r="H280" t="inlineStr">
         <is>
           <t>False Negative</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>BLEU = 0.43 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 124.000 hyp_len = 124 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -12993,11 +11569,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -13036,11 +11607,6 @@
       <c r="H282" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -13083,11 +11649,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13128,11 +11689,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13174,11 +11730,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13217,11 +11768,6 @@
       <c r="H286" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -13264,11 +11810,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13307,11 +11848,6 @@
       <c r="H288" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -13354,11 +11890,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13399,11 +11930,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>BLEU = 0.62 6.6/0.6/0.3/0.1 (BP = 1.000 ratio = 91.000 hyp_len = 91 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13444,11 +11970,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13489,11 +12010,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13534,11 +12050,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13579,11 +12090,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13624,11 +12130,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -13669,11 +12170,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -13714,11 +12210,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -13759,11 +12250,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -13804,11 +12290,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -13849,11 +12330,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>BLEU = 0.65 6.9/0.6/0.3/0.1 (BP = 1.000 ratio = 87.000 hyp_len = 87 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -13893,11 +12369,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -13937,11 +12408,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -13981,11 +12447,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14025,11 +12486,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14067,11 +12523,6 @@
       <c r="H305" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -14113,11 +12564,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14157,11 +12603,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14201,11 +12642,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14245,11 +12681,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14289,11 +12720,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>BLEU = 0.42 4.0/0.4/0.2/0.1 (BP = 1.000 ratio = 126.000 hyp_len = 126 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14333,11 +12759,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14377,11 +12798,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14421,11 +12837,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14465,11 +12876,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14509,11 +12915,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -14553,11 +12954,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -14595,11 +12991,6 @@
       <c r="H317" t="inlineStr">
         <is>
           <t>True Negative</t>
-        </is>
-      </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -14641,11 +13032,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14685,11 +13071,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -14729,11 +13110,6 @@
           <t>True Negative</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>BLEU = 0.40 3.8/0.4/0.2/0.1 (BP = 1.000 ratio = 133.000 hyp_len = 133 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -14774,11 +13150,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -14817,11 +13188,6 @@
       <c r="H322" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -14864,11 +13230,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -14909,11 +13270,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -14952,11 +13308,6 @@
       <c r="H325" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15003,11 +13354,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -15048,11 +13394,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15093,11 +13434,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15138,11 +13474,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15183,11 +13514,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>BLEU = 0.48 5.2/0.4/0.2/0.1 (BP = 1.000 ratio = 116.000 hyp_len = 116 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15229,11 +13555,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15276,11 +13597,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15322,11 +13638,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15368,11 +13679,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15413,11 +13719,6 @@
       <c r="H335" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15464,11 +13765,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15510,11 +13806,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -15554,11 +13845,6 @@
       <c r="H338" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15599,11 +13885,6 @@
       <c r="H339" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15652,11 +13933,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>BLEU = 0.34 3.6/0.3/0.2/0.1 (BP = 1.000 ratio = 165.000 hyp_len = 165 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -15668,7 +13944,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -15679,13 +13955,13 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0.8655986785888672</v>
+        <v>0.8709112405776978</v>
       </c>
       <c r="E341" t="n">
-        <v>0.9259120225906372</v>
+        <v>0.9351852536201477</v>
       </c>
       <c r="F341" t="n">
-        <v>0.8947400450706482</v>
+        <v>0.9019045829772949</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -15695,11 +13971,6 @@
       <c r="H341" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15713,7 +13984,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15724,13 +13995,13 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>0.8906223177909851</v>
+        <v>0.8930139541625977</v>
       </c>
       <c r="E342" t="n">
-        <v>0.9222061038017273</v>
+        <v>0.9300037026405334</v>
       </c>
       <c r="F342" t="n">
-        <v>0.906139075756073</v>
+        <v>0.9111335873603821</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -15740,11 +14011,6 @@
       <c r="H342" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15758,7 +14024,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -15769,13 +14035,13 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>0.856173574924469</v>
+        <v>0.8584775328636169</v>
       </c>
       <c r="E343" t="n">
-        <v>0.9279747009277344</v>
+        <v>0.9338434338569641</v>
       </c>
       <c r="F343" t="n">
-        <v>0.8906294107437134</v>
+        <v>0.8945759534835815</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -15785,11 +14051,6 @@
       <c r="H343" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15803,7 +14064,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -15814,13 +14075,13 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>0.8670542240142822</v>
+        <v>0.8705359101295471</v>
       </c>
       <c r="E344" t="n">
-        <v>0.9238986372947693</v>
+        <v>0.9323393702507019</v>
       </c>
       <c r="F344" t="n">
-        <v>0.8945742845535278</v>
+        <v>0.9003782868385315</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -15830,11 +14091,6 @@
       <c r="H344" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15848,7 +14104,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -15859,13 +14115,13 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0.8484592437744141</v>
+        <v>0.8513299822807312</v>
       </c>
       <c r="E345" t="n">
-        <v>0.9228818416595459</v>
+        <v>0.9318398237228394</v>
       </c>
       <c r="F345" t="n">
-        <v>0.8841071128845215</v>
+        <v>0.8897674679756165</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
@@ -15875,11 +14131,6 @@
       <c r="H345" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15893,7 +14144,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -15904,13 +14155,13 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>0.8566431999206543</v>
+        <v>0.8593124151229858</v>
       </c>
       <c r="E346" t="n">
-        <v>0.9195066094398499</v>
+        <v>0.9281324148178101</v>
       </c>
       <c r="F346" t="n">
-        <v>0.8869624733924866</v>
+        <v>0.8923975229263306</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
@@ -15920,11 +14171,6 @@
       <c r="H346" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15938,7 +14184,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -15949,13 +14195,13 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0.8593063950538635</v>
+        <v>0.8636053800582886</v>
       </c>
       <c r="E347" t="n">
-        <v>0.9247097373008728</v>
+        <v>0.932431161403656</v>
       </c>
       <c r="F347" t="n">
-        <v>0.8908092379570007</v>
+        <v>0.8966995477676392</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -15965,11 +14211,6 @@
       <c r="H347" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -15983,7 +14224,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15994,13 +14235,13 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>0.8487001657485962</v>
+        <v>0.8528486490249634</v>
       </c>
       <c r="E348" t="n">
-        <v>0.9098653793334961</v>
+        <v>0.9188830852508545</v>
       </c>
       <c r="F348" t="n">
-        <v>0.8782190680503845</v>
+        <v>0.884635329246521</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -16010,11 +14251,6 @@
       <c r="H348" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -16028,7 +14264,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -16039,13 +14275,13 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.841772198677063</v>
+        <v>0.8438159227371216</v>
       </c>
       <c r="E349" t="n">
-        <v>0.9163633584976196</v>
+        <v>0.9258427023887634</v>
       </c>
       <c r="F349" t="n">
-        <v>0.8774855136871338</v>
+        <v>0.8829283118247986</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -16055,11 +14291,6 @@
       <c r="H349" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -16073,7 +14304,7 @@
         <is>
           <t>1. Person Found.
 2. Person Requires Immediate Assistance
-3. Assistance needed: First respondered should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
+3. Assistance needed: First responders should be deployed immediately to return the man inside the building or provide a surface to catch the man safely.</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -16084,13 +14315,13 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0.8577486276626587</v>
+        <v>0.8592146635055542</v>
       </c>
       <c r="E350" t="n">
-        <v>0.9213781356811523</v>
+        <v>0.9296556711196899</v>
       </c>
       <c r="F350" t="n">
-        <v>0.8884255886077881</v>
+        <v>0.8930482268333435</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -16100,11 +14331,6 @@
       <c r="H350" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>BLEU = 0.49 5.9/0.4/0.2/0.1 (BP = 1.000 ratio = 118.000 hyp_len = 118 ref_len = 1)</t>
         </is>
       </c>
     </row>
@@ -16147,11 +14373,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16192,11 +14413,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -16237,11 +14453,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -16282,11 +14493,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16327,11 +14533,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -16372,11 +14573,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16417,11 +14613,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16462,11 +14653,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16507,11 +14693,6 @@
           <t>True Positive</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -16550,11 +14731,6 @@
       <c r="H360" t="inlineStr">
         <is>
           <t>True Positive</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>BLEU = 0.55 5.8/0.5/0.2/0.1 (BP = 1.000 ratio = 103.000 hyp_len = 103 ref_len = 1)</t>
         </is>
       </c>
     </row>
